--- a/artfynd/A 13006-2024 artfynd.xlsx
+++ b/artfynd/A 13006-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>88987388</v>
       </c>
       <c r="B2" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537719.0460869211</v>
+        <v>537719</v>
       </c>
       <c r="R2" t="n">
-        <v>6350887.78695458</v>
+        <v>6350888</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2020-09-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88987383</v>
+        <v>88987418</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,35 +799,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102421</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slåttergubbemal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Digitivalva arnicella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(von Heyden, 1863)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -855,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537719.0460869211</v>
+        <v>537938</v>
       </c>
       <c r="R3" t="n">
-        <v>6350887.78695458</v>
+        <v>6350717</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,19 +865,14 @@
           <t>2020-09-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>minor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,15 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116488779</v>
+        <v>88987414</v>
       </c>
       <c r="B4" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,34 +915,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219955</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hultsfred (Hultsfred), Sm</t>
+          <t>Ramsebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537729</v>
+        <v>537938</v>
       </c>
       <c r="R4" t="n">
-        <v>6350879</v>
+        <v>6350717</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,17 +981,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Närmare 100 plantor</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,33 +995,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116489673</v>
+        <v>88987367</v>
       </c>
       <c r="B5" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,19 +1048,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hultsfred (Hultsfred), Sm</t>
+          <t>Ramsebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537719</v>
+        <v>537703</v>
       </c>
       <c r="R5" t="n">
-        <v>6350852</v>
+        <v>6350909</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,12 +1095,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,21 +1109,449 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>88987383</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ramsebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>537719</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6350888</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>116488779</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>537729</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6350879</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Närmare 100 plantor</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>116489673</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>537719</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6350852</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>88987399</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ramsebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>537919</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6350773</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13006-2024 artfynd.xlsx
+++ b/artfynd/A 13006-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88987388</t>
         </is>
       </c>
     </row>
@@ -901,6 +911,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88987418</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88987414</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88987367</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,6 +1268,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88987383</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1345,6 +1375,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116488779</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116489673</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,8 +1592,23 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88987399</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>